--- a/SuppXLS/Scen_UC_Costupdate.xlsx
+++ b/SuppXLS/Scen_UC_Costupdate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63D92BD-D724-451E-9082-C452E0334DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75F1AB3-004F-4C05-AADA-FD7851922192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{11B4A3C4-816A-4862-A163-A26D2ADE20D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{11B4A3C4-816A-4862-A163-A26D2ADE20D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Costupdate" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>TimeSlice</t>
   </si>
@@ -104,10 +104,16 @@
     <t>CSP</t>
   </si>
   <si>
-    <t>*0.8</t>
-  </si>
-  <si>
     <t>INVCOST</t>
+  </si>
+  <si>
+    <t>*0.56</t>
+  </si>
+  <si>
+    <t>*0.82</t>
+  </si>
+  <si>
+    <t>*0.9</t>
   </si>
 </sst>
 </file>
@@ -686,10 +692,10 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
         <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
       </c>
       <c r="K3" t="s">
         <v>17</v>
@@ -697,10 +703,10 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
@@ -708,10 +714,10 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
         <v>19</v>
